--- a/data/raw/sales/Week 13/Fossil/amazon_sales.xlsx
+++ b/data/raw/sales/Week 13/Fossil/amazon_sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 13\Fossil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59733C7D-2819-4099-B43E-2476F9B572E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC75274-12BF-41C2-8C0C-DEB9B27960B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A25441FF-179A-4E9E-968A-432FC427024C}"/>
   </bookViews>
@@ -18,7 +18,18 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cambium R'!$A$1:$W$342</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -5024,10 +5035,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D595F3A6-433B-4A17-BBFE-F9076B3B211E}">
-  <dimension ref="A1:W342"/>
+  <dimension ref="A1:X342"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="20" max="20" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>701</v>
       </c>
@@ -5098,7 +5113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1365</v>
       </c>
@@ -5157,7 +5172,7 @@
         <v>4.5499999999999999E-2</v>
       </c>
       <c r="T2" s="3">
-        <v>362115</v>
+        <v>306877.11864406778</v>
       </c>
       <c r="U2" s="3">
         <v>24141</v>
@@ -5168,8 +5183,9 @@
       <c r="W2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X2" s="3"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>711</v>
       </c>
@@ -5228,7 +5244,7 @@
         <v>1.7399999999999999E-2</v>
       </c>
       <c r="T3" s="3">
-        <v>481471</v>
+        <v>408026.27118644072</v>
       </c>
       <c r="U3" s="3">
         <v>33591</v>
@@ -5239,8 +5255,9 @@
       <c r="W3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X3" s="3"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>709</v>
       </c>
@@ -5299,7 +5316,7 @@
         <v>1.67E-2</v>
       </c>
       <c r="T4" s="3">
-        <v>434820</v>
+        <v>368491.52542372886</v>
       </c>
       <c r="U4" s="3">
         <v>57976</v>
@@ -5310,8 +5327,9 @@
       <c r="W4">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X4" s="3"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>733</v>
       </c>
@@ -5370,7 +5388,7 @@
         <v>3.5700000000000003E-2</v>
       </c>
       <c r="T5" s="3">
-        <v>265804</v>
+        <v>225257.62711864407</v>
       </c>
       <c r="U5" s="3">
         <v>9493</v>
@@ -5381,8 +5399,9 @@
       <c r="W5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X5" s="3"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>715</v>
       </c>
@@ -5441,7 +5460,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>142410</v>
+        <v>120686.44067796611</v>
       </c>
       <c r="U6" s="3">
         <v>0</v>
@@ -5452,8 +5471,9 @@
       <c r="W6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X6" s="3"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>865</v>
       </c>
@@ -5512,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="T7" s="3">
-        <v>118767</v>
+        <v>100650</v>
       </c>
       <c r="U7" s="3">
         <v>0</v>
@@ -5523,8 +5543,9 @@
       <c r="W7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X7" s="3"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>725</v>
       </c>
@@ -5583,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>81176</v>
+        <v>68793.220338983054</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -5594,8 +5615,9 @@
       <c r="W8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X8" s="3"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>729</v>
       </c>
@@ -5654,7 +5676,7 @@
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>95960</v>
+        <v>81322.03389830509</v>
       </c>
       <c r="U9" s="3">
         <v>0</v>
@@ -5665,8 +5687,9 @@
       <c r="W9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X9" s="3"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>917</v>
       </c>
@@ -5725,7 +5748,7 @@
         <v>9.2999999999999992E-3</v>
       </c>
       <c r="T10" s="3">
-        <v>101465</v>
+        <v>85987.288135593219</v>
       </c>
       <c r="U10" s="3">
         <v>14495</v>
@@ -5736,8 +5759,9 @@
       <c r="W10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X10" s="3"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>801</v>
       </c>
@@ -5796,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="3">
-        <v>80964</v>
+        <v>68613.559322033907</v>
       </c>
       <c r="U11" s="3">
         <v>0</v>
@@ -5807,8 +5831,9 @@
       <c r="W11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>721</v>
       </c>
@@ -5867,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="3">
-        <v>49975</v>
+        <v>42351.694915254237</v>
       </c>
       <c r="U12" s="3">
         <v>0</v>
@@ -5878,8 +5903,9 @@
       <c r="W12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X12" s="3"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>739</v>
       </c>
@@ -5938,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="3">
-        <v>122470</v>
+        <v>103788.13559322034</v>
       </c>
       <c r="U13" s="3">
         <v>0</v>
@@ -5949,8 +5975,9 @@
       <c r="W13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X13" s="3"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>753</v>
       </c>
@@ -6009,7 +6036,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
-        <v>47235</v>
+        <v>40029.661016949154</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -6020,8 +6047,9 @@
       <c r="W14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X14" s="3"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>737</v>
       </c>
@@ -6080,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="3">
-        <v>79975</v>
+        <v>67775.423728813563</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -6091,8 +6119,9 @@
       <c r="W15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X15" s="3"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>875</v>
       </c>
@@ -6151,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="3">
-        <v>39975</v>
+        <v>33877.118644067799</v>
       </c>
       <c r="U16" s="3">
         <v>0</v>
@@ -6162,8 +6191,9 @@
       <c r="W16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>743</v>
       </c>
@@ -6222,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="3">
-        <v>36383</v>
+        <v>30833.050847457627</v>
       </c>
       <c r="U17" s="3">
         <v>0</v>
@@ -6233,8 +6263,9 @@
       <c r="W17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X17" s="3"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>749</v>
       </c>
@@ -6293,7 +6324,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="3">
-        <v>57976</v>
+        <v>49132.203389830509</v>
       </c>
       <c r="U18" s="3">
         <v>0</v>
@@ -6304,8 +6335,9 @@
       <c r="W18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X18" s="3"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>741</v>
       </c>
@@ -6364,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="3">
-        <v>63976</v>
+        <v>54216.949152542373</v>
       </c>
       <c r="U19" s="3">
         <v>0</v>
@@ -6375,8 +6407,9 @@
       <c r="W19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>759</v>
       </c>
@@ -6435,7 +6468,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>57976</v>
+        <v>49132.203389830509</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -6446,8 +6479,9 @@
       <c r="W20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X20" s="3"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>765</v>
       </c>
@@ -6506,7 +6540,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="3">
-        <v>51976</v>
+        <v>44047.457627118645</v>
       </c>
       <c r="U21" s="3">
         <v>0</v>
@@ -6517,8 +6551,9 @@
       <c r="W21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X21" s="3"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>723</v>
       </c>
@@ -6577,7 +6612,7 @@
         <v>3.0300000000000001E-2</v>
       </c>
       <c r="T22" s="3">
-        <v>63976</v>
+        <v>54216.949152542373</v>
       </c>
       <c r="U22" s="3">
         <v>15994</v>
@@ -6588,8 +6623,9 @@
       <c r="W22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X22" s="3"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>807</v>
       </c>
@@ -6648,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="T23" s="3">
-        <v>53980</v>
+        <v>45745.762711864409</v>
       </c>
       <c r="U23" s="3">
         <v>0</v>
@@ -6659,8 +6695,9 @@
       <c r="W23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X23" s="3"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>757</v>
       </c>
@@ -6719,7 +6756,7 @@
         <v>8.3299999999999999E-2</v>
       </c>
       <c r="T24" s="3">
-        <v>68982</v>
+        <v>58459.322033898308</v>
       </c>
       <c r="U24" s="3">
         <v>22994</v>
@@ -6730,8 +6767,9 @@
       <c r="W24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X24" s="3"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>735</v>
       </c>
@@ -6790,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="T25" s="3">
-        <v>35982</v>
+        <v>30493.220338983054</v>
       </c>
       <c r="U25" s="3">
         <v>0</v>
@@ -6801,8 +6839,9 @@
       <c r="W25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X25" s="3"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>793</v>
       </c>
@@ -6861,7 +6900,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="3">
-        <v>38982</v>
+        <v>33035.593220338982</v>
       </c>
       <c r="U26" s="3">
         <v>0</v>
@@ -6872,8 +6911,9 @@
       <c r="W26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X26" s="3"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>719</v>
       </c>
@@ -6932,7 +6972,7 @@
         <v>4.1700000000000001E-2</v>
       </c>
       <c r="T27" s="3">
-        <v>38982</v>
+        <v>33035.593220338982</v>
       </c>
       <c r="U27" s="3">
         <v>12994</v>
@@ -6943,8 +6983,9 @@
       <c r="W27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X27" s="3"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1065</v>
       </c>
@@ -7003,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="3">
-        <v>27291</v>
+        <v>23127.966101694918</v>
       </c>
       <c r="U28" s="3">
         <v>0</v>
@@ -7014,8 +7055,9 @@
       <c r="W28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X28" s="3"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1057</v>
       </c>
@@ -7074,7 +7116,7 @@
         <v>5.2600000000000001E-2</v>
       </c>
       <c r="T29" s="3">
-        <v>28341</v>
+        <v>24017.796610169491</v>
       </c>
       <c r="U29" s="3">
         <v>9447</v>
@@ -7085,8 +7127,9 @@
       <c r="W29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X29" s="3"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>775</v>
       </c>
@@ -7145,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="3">
-        <v>59982</v>
+        <v>50832.203389830509</v>
       </c>
       <c r="U30" s="3">
         <v>0</v>
@@ -7156,8 +7199,9 @@
       <c r="W30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X30" s="3"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1367</v>
       </c>
@@ -7216,7 +7260,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="3">
-        <v>27891</v>
+        <v>23636.440677966104</v>
       </c>
       <c r="U31" s="3">
         <v>0</v>
@@ -7227,8 +7271,9 @@
       <c r="W31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X31" s="3"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>727</v>
       </c>
@@ -7287,7 +7332,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>38982</v>
+        <v>33035.593220338982</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
@@ -7298,8 +7343,9 @@
       <c r="W32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X32" s="3"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>955</v>
       </c>
@@ -7358,7 +7404,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="3">
-        <v>65982</v>
+        <v>55916.949152542373</v>
       </c>
       <c r="U33" s="3">
         <v>0</v>
@@ -7369,8 +7415,9 @@
       <c r="W33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X33" s="3"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>869</v>
       </c>
@@ -7429,7 +7476,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="3">
-        <v>55185</v>
+        <v>46766.949152542373</v>
       </c>
       <c r="U34" s="3">
         <v>0</v>
@@ -7440,8 +7487,9 @@
       <c r="W34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X34" s="3"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>773</v>
       </c>
@@ -7500,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="3">
-        <v>40473</v>
+        <v>34299.152542372882</v>
       </c>
       <c r="U35" s="3">
         <v>0</v>
@@ -7511,8 +7559,9 @@
       <c r="W35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X35" s="3"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>843</v>
       </c>
@@ -7571,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="3">
-        <v>30438</v>
+        <v>25794.91525423729</v>
       </c>
       <c r="U36" s="3">
         <v>0</v>
@@ -7582,8 +7631,9 @@
       <c r="W36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X36" s="3"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>745</v>
       </c>
@@ -7642,7 +7692,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="3">
-        <v>43482</v>
+        <v>36849.152542372882</v>
       </c>
       <c r="U37" s="3">
         <v>0</v>
@@ -7653,8 +7703,9 @@
       <c r="W37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X37" s="3"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1267</v>
       </c>
@@ -7713,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="3">
-        <v>35985</v>
+        <v>30495.762711864409</v>
       </c>
       <c r="U38" s="3">
         <v>0</v>
@@ -7724,8 +7775,9 @@
       <c r="W38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X38" s="3"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1067</v>
       </c>
@@ -7784,7 +7836,7 @@
         <v>0</v>
       </c>
       <c r="T39" s="3">
-        <v>25990</v>
+        <v>22025.423728813559</v>
       </c>
       <c r="U39" s="3">
         <v>0</v>
@@ -7795,8 +7847,9 @@
       <c r="W39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>925</v>
       </c>
@@ -7855,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="3">
-        <v>28988</v>
+        <v>24566.101694915254</v>
       </c>
       <c r="U40" s="3">
         <v>0</v>
@@ -7866,8 +7919,9 @@
       <c r="W40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>731</v>
       </c>
@@ -7926,7 +7980,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="3">
-        <v>28988</v>
+        <v>24566.101694915254</v>
       </c>
       <c r="U41" s="3">
         <v>0</v>
@@ -7937,8 +7991,9 @@
       <c r="W41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X41" s="3"/>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1375</v>
       </c>
@@ -7997,7 +8052,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="3">
-        <v>20294</v>
+        <v>17198.305084745763</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -8008,8 +8063,9 @@
       <c r="W42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X42" s="3"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>751</v>
       </c>
@@ -8068,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
-        <v>25988</v>
+        <v>22023.728813559323</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -8079,8 +8135,9 @@
       <c r="W43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X43" s="3"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>777</v>
       </c>
@@ -8139,7 +8196,7 @@
         <v>0.1111</v>
       </c>
       <c r="T44" s="3">
-        <v>23988</v>
+        <v>20328.813559322036</v>
       </c>
       <c r="U44" s="3">
         <v>11994</v>
@@ -8150,8 +8207,9 @@
       <c r="W44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X44" s="3"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>787</v>
       </c>
@@ -8210,7 +8268,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="3">
-        <v>41988</v>
+        <v>35583.050847457627</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -8221,8 +8279,9 @@
       <c r="W45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X45" s="3"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" t="e">
         <v>#N/A</v>
       </c>
@@ -8281,7 +8340,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="3">
-        <v>34990</v>
+        <v>29652.542372881358</v>
       </c>
       <c r="U46" s="3">
         <v>0</v>
@@ -8292,8 +8351,9 @@
       <c r="W46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X46" s="3"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>803</v>
       </c>
@@ -8352,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="3">
-        <v>31988</v>
+        <v>27108.474576271186</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -8363,8 +8423,9 @@
       <c r="W47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X47" s="3"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>781</v>
       </c>
@@ -8423,7 +8484,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="3">
-        <v>31988</v>
+        <v>27108.474576271186</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -8434,8 +8495,9 @@
       <c r="W48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X48" s="3"/>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>819</v>
       </c>
@@ -8494,7 +8556,7 @@
         <v>0</v>
       </c>
       <c r="T49" s="3">
-        <v>26988</v>
+        <v>22871.186440677968</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -8505,8 +8567,9 @@
       <c r="W49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X49" s="3"/>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>763</v>
       </c>
@@ -8565,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="T50" s="3">
-        <v>23980</v>
+        <v>20322.033898305086</v>
       </c>
       <c r="U50" s="3">
         <v>0</v>
@@ -8576,8 +8639,9 @@
       <c r="W50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X50" s="3"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1149</v>
       </c>
@@ -8636,7 +8700,7 @@
         <v>0</v>
       </c>
       <c r="T51" s="3">
-        <v>39988</v>
+        <v>33888.135593220344</v>
       </c>
       <c r="U51" s="3">
         <v>0</v>
@@ -8647,8 +8711,9 @@
       <c r="W51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X51" s="3"/>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>785</v>
       </c>
@@ -8707,7 +8772,7 @@
         <v>0</v>
       </c>
       <c r="T52" s="3">
-        <v>26988</v>
+        <v>22871.186440677968</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -8718,8 +8783,9 @@
       <c r="W52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X52" s="3"/>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>1261</v>
       </c>
@@ -8778,7 +8844,7 @@
         <v>0</v>
       </c>
       <c r="T53" s="3">
-        <v>26990</v>
+        <v>22872.881355932204</v>
       </c>
       <c r="U53" s="3">
         <v>0</v>
@@ -8789,8 +8855,9 @@
       <c r="W53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X53" s="3"/>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>911</v>
       </c>
@@ -8849,7 +8916,7 @@
         <v>0</v>
       </c>
       <c r="T54" s="3">
-        <v>48990</v>
+        <v>41516.949152542373</v>
       </c>
       <c r="U54" s="3">
         <v>0</v>
@@ -8860,8 +8927,9 @@
       <c r="W54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X54" s="3"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1047</v>
       </c>
@@ -8920,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="3">
-        <v>31988</v>
+        <v>27108.474576271186</v>
       </c>
       <c r="U55" s="3">
         <v>0</v>
@@ -8931,8 +8999,9 @@
       <c r="W55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>825</v>
       </c>
@@ -8991,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="3">
-        <v>28988</v>
+        <v>24566.101694915254</v>
       </c>
       <c r="U56" s="3">
         <v>0</v>
@@ -9002,8 +9071,9 @@
       <c r="W56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>871</v>
       </c>
@@ -9062,7 +9132,7 @@
         <v>0</v>
       </c>
       <c r="T57" s="3">
-        <v>31990</v>
+        <v>27110.169491525427</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -9073,8 +9143,9 @@
       <c r="W57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X57" s="3"/>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>895</v>
       </c>
@@ -9133,7 +9204,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>31990</v>
+        <v>27110.169491525427</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -9144,8 +9215,9 @@
       <c r="W58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X58" s="3"/>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>853</v>
       </c>
@@ -9204,7 +9276,7 @@
         <v>0</v>
       </c>
       <c r="T59" s="3">
-        <v>28990</v>
+        <v>24567.796610169491</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
@@ -9215,8 +9287,9 @@
       <c r="W59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X59" s="3"/>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>919</v>
       </c>
@@ -9275,7 +9348,7 @@
         <v>2.9399999999999999E-2</v>
       </c>
       <c r="T60" s="3">
-        <v>39988</v>
+        <v>33888.135593220344</v>
       </c>
       <c r="U60" s="3">
         <v>19994</v>
@@ -9286,8 +9359,9 @@
       <c r="W60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X60" s="3"/>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>1205</v>
       </c>
@@ -9346,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>26990</v>
+        <v>22872.881355932204</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -9357,8 +9431,9 @@
       <c r="W61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X61" s="3"/>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>1247</v>
       </c>
@@ -9417,7 +9492,7 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
-        <v>23990</v>
+        <v>20330.508474576272</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -9428,8 +9503,9 @@
       <c r="W62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X62" s="3"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>1343</v>
       </c>
@@ -9488,7 +9564,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="3">
-        <v>39990</v>
+        <v>33889.830508474581</v>
       </c>
       <c r="U63" s="3">
         <v>0</v>
@@ -9499,8 +9575,9 @@
       <c r="W63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X63" s="3"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>1315</v>
       </c>
@@ -9559,7 +9636,7 @@
         <v>0</v>
       </c>
       <c r="T64" s="3">
-        <v>25990</v>
+        <v>22025.423728813559</v>
       </c>
       <c r="U64" s="3">
         <v>0</v>
@@ -9570,8 +9647,9 @@
       <c r="W64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X64" s="3"/>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>713</v>
       </c>
@@ -9630,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="T65" s="3">
-        <v>13494</v>
+        <v>11435.593220338984</v>
       </c>
       <c r="U65" s="3">
         <v>0</v>
@@ -9641,8 +9719,9 @@
       <c r="W65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X65" s="3"/>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>717</v>
       </c>
@@ -9701,7 +9780,7 @@
         <v>0</v>
       </c>
       <c r="T66" s="3">
-        <v>12994</v>
+        <v>11011.864406779661</v>
       </c>
       <c r="U66" s="3">
         <v>0</v>
@@ -9712,8 +9791,9 @@
       <c r="W66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X66" s="3"/>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>761</v>
       </c>
@@ -9772,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="T67" s="3">
-        <v>12994</v>
+        <v>11011.864406779661</v>
       </c>
       <c r="U67" s="3">
         <v>0</v>
@@ -9783,8 +9863,9 @@
       <c r="W67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>1381</v>
       </c>
@@ -9843,7 +9924,7 @@
         <v>0</v>
       </c>
       <c r="T68" s="3">
-        <v>14495</v>
+        <v>12283.898305084746</v>
       </c>
       <c r="U68" s="3">
         <v>0</v>
@@ -9854,8 +9935,9 @@
       <c r="W68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X68" s="3"/>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>1331</v>
       </c>
@@ -9914,7 +9996,7 @@
         <v>0</v>
       </c>
       <c r="T69" s="3">
-        <v>20495</v>
+        <v>17368.644067796609</v>
       </c>
       <c r="U69" s="3">
         <v>0</v>
@@ -9925,8 +10007,9 @@
       <c r="W69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X69" s="3"/>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>1223</v>
       </c>
@@ -9985,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>10497</v>
+        <v>8895.7627118644068</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
@@ -9996,8 +10079,9 @@
       <c r="W70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X70" s="3"/>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>923</v>
       </c>
@@ -10056,7 +10140,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="3">
-        <v>15494</v>
+        <v>13130.508474576272</v>
       </c>
       <c r="U71" s="3">
         <v>0</v>
@@ -10067,8 +10151,9 @@
       <c r="W71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X71" s="3"/>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>1371</v>
       </c>
@@ -10127,7 +10212,7 @@
         <v>0</v>
       </c>
       <c r="T72" s="3">
-        <v>8047</v>
+        <v>6819.4915254237294</v>
       </c>
       <c r="U72" s="3">
         <v>0</v>
@@ -10138,8 +10223,9 @@
       <c r="W72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X72" s="3"/>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>809</v>
       </c>
@@ -10198,7 +10284,7 @@
         <v>0</v>
       </c>
       <c r="T73" s="3">
-        <v>20494</v>
+        <v>17367.796610169491</v>
       </c>
       <c r="U73" s="3">
         <v>0</v>
@@ -10209,8 +10295,9 @@
       <c r="W73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X73" s="3"/>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>821</v>
       </c>
@@ -10269,7 +10356,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="3">
-        <v>13494</v>
+        <v>11435.593220338984</v>
       </c>
       <c r="U74" s="3">
         <v>0</v>
@@ -10280,8 +10367,9 @@
       <c r="W74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X74" s="3"/>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>805</v>
       </c>
@@ -10340,7 +10428,7 @@
         <v>0</v>
       </c>
       <c r="T75" s="3">
-        <v>22994</v>
+        <v>19486.440677966104</v>
       </c>
       <c r="U75" s="3">
         <v>0</v>
@@ -10351,8 +10439,9 @@
       <c r="W75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X75" s="3"/>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>889</v>
       </c>
@@ -10411,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="3">
-        <v>19995</v>
+        <v>16944.91525423729</v>
       </c>
       <c r="U76" s="3">
         <v>0</v>
@@ -10422,8 +10511,9 @@
       <c r="W76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X76" s="3"/>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>971</v>
       </c>
@@ -10482,7 +10572,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="3">
-        <v>12246</v>
+        <v>10377.966101694916</v>
       </c>
       <c r="U77" s="3">
         <v>0</v>
@@ -10493,8 +10583,9 @@
       <c r="W77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X77" s="3"/>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>835</v>
       </c>
@@ -10553,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="3">
-        <v>11994</v>
+        <v>10164.406779661018</v>
       </c>
       <c r="U78" s="3">
         <v>0</v>
@@ -10564,8 +10655,9 @@
       <c r="W78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X78" s="3"/>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>937</v>
       </c>
@@ -10624,7 +10716,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="3">
-        <v>17994</v>
+        <v>15249.152542372882</v>
       </c>
       <c r="U79" s="3">
         <v>0</v>
@@ -10635,8 +10727,9 @@
       <c r="W79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X79" s="3"/>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>779</v>
       </c>
@@ -10695,7 +10788,7 @@
         <v>0</v>
       </c>
       <c r="T80" s="3">
-        <v>15994</v>
+        <v>13554.237288135593</v>
       </c>
       <c r="U80" s="3">
         <v>0</v>
@@ -10706,8 +10799,9 @@
       <c r="W80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X80" s="3"/>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>799</v>
       </c>
@@ -10766,7 +10860,7 @@
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <v>11993</v>
+        <v>10163.5593220339</v>
       </c>
       <c r="U81" s="3">
         <v>0</v>
@@ -10777,8 +10871,9 @@
       <c r="W81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X81" s="3"/>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>789</v>
       </c>
@@ -10837,7 +10932,7 @@
         <v>0</v>
       </c>
       <c r="T82" s="3">
-        <v>21994</v>
+        <v>18638.983050847459</v>
       </c>
       <c r="U82" s="3">
         <v>0</v>
@@ -10848,8 +10943,9 @@
       <c r="W82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>953</v>
       </c>
@@ -10908,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>11994</v>
+        <v>10164.406779661018</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -10919,8 +11015,9 @@
       <c r="W83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X83" s="3"/>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>1031</v>
       </c>
@@ -10979,7 +11076,7 @@
         <v>0</v>
       </c>
       <c r="T84" s="3">
-        <v>13197</v>
+        <v>11183.898305084746</v>
       </c>
       <c r="U84" s="3">
         <v>0</v>
@@ -10990,8 +11087,9 @@
       <c r="W84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X84" s="3"/>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>921</v>
       </c>
@@ -11050,7 +11148,7 @@
         <v>0</v>
       </c>
       <c r="T85" s="3">
-        <v>15994</v>
+        <v>13554.237288135593</v>
       </c>
       <c r="U85" s="3">
         <v>0</v>
@@ -11061,8 +11159,9 @@
       <c r="W85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X85" s="3"/>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>947</v>
       </c>
@@ -11121,7 +11220,7 @@
         <v>0</v>
       </c>
       <c r="T86" s="3">
-        <v>11994</v>
+        <v>10164.406779661018</v>
       </c>
       <c r="U86" s="3">
         <v>0</v>
@@ -11132,8 +11231,9 @@
       <c r="W86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X86" s="3"/>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>1053</v>
       </c>
@@ -11192,7 +11292,7 @@
         <v>0</v>
       </c>
       <c r="T87" s="3">
-        <v>19995</v>
+        <v>16944.91525423729</v>
       </c>
       <c r="U87" s="3">
         <v>0</v>
@@ -11203,8 +11303,9 @@
       <c r="W87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X87" s="3"/>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>811</v>
       </c>
@@ -11263,7 +11364,7 @@
         <v>0</v>
       </c>
       <c r="T88" s="3">
-        <v>10146</v>
+        <v>8598.3050847457635</v>
       </c>
       <c r="U88" s="3">
         <v>0</v>
@@ -11274,8 +11375,9 @@
       <c r="W88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X88" s="3"/>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>1085</v>
       </c>
@@ -11334,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="T89" s="3">
-        <v>15995</v>
+        <v>13555.084745762713</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
@@ -11345,8 +11447,9 @@
       <c r="W89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X89" s="3"/>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>1079</v>
       </c>
@@ -11405,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="T90" s="3">
-        <v>8397</v>
+        <v>7116.1016949152545</v>
       </c>
       <c r="U90" s="3">
         <v>0</v>
@@ -11416,8 +11519,9 @@
       <c r="W90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>887</v>
       </c>
@@ -11476,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
-        <v>15995</v>
+        <v>13555.084745762713</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -11487,8 +11591,9 @@
       <c r="W91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X91" s="3"/>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>929</v>
       </c>
@@ -11547,7 +11652,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="3">
-        <v>19995</v>
+        <v>16944.91525423729</v>
       </c>
       <c r="U92" s="3">
         <v>0</v>
@@ -11558,8 +11663,9 @@
       <c r="W92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X92" s="3"/>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>1115</v>
       </c>
@@ -11618,7 +11724,7 @@
         <v>0</v>
       </c>
       <c r="T93" s="3">
-        <v>12297</v>
+        <v>10421.186440677966</v>
       </c>
       <c r="U93" s="3">
         <v>0</v>
@@ -11629,8 +11735,9 @@
       <c r="W93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X93" s="3"/>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>1111</v>
       </c>
@@ -11689,7 +11796,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
-        <v>11498</v>
+        <v>9744.0677966101703</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -11700,8 +11807,9 @@
       <c r="W94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X94" s="3"/>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>1113</v>
       </c>
@@ -11760,7 +11868,7 @@
         <v>0</v>
       </c>
       <c r="T95" s="3">
-        <v>11498</v>
+        <v>9744.0677966101703</v>
       </c>
       <c r="U95" s="3">
         <v>0</v>
@@ -11771,8 +11879,9 @@
       <c r="W95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>1109</v>
       </c>
@@ -11831,7 +11940,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
-        <v>11498</v>
+        <v>9744.0677966101703</v>
       </c>
       <c r="U96" s="3">
         <v>0</v>
@@ -11842,8 +11951,9 @@
       <c r="W96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X96" s="3"/>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>755</v>
       </c>
@@ -11902,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="T97" s="3">
-        <v>23991</v>
+        <v>20331.355932203391</v>
       </c>
       <c r="U97" s="3">
         <v>0</v>
@@ -11913,8 +12023,9 @@
       <c r="W97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X97" s="3"/>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>927</v>
       </c>
@@ -11973,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="T98" s="3">
-        <v>15995</v>
+        <v>13555.084745762713</v>
       </c>
       <c r="U98" s="3">
         <v>0</v>
@@ -11984,8 +12095,9 @@
       <c r="W98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X98" s="3"/>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>987</v>
       </c>
@@ -12044,7 +12156,7 @@
         <v>0</v>
       </c>
       <c r="T99" s="3">
-        <v>18495</v>
+        <v>15673.728813559323</v>
       </c>
       <c r="U99" s="3">
         <v>0</v>
@@ -12055,8 +12167,9 @@
       <c r="W99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X99" s="3"/>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>1377</v>
       </c>
@@ -12115,7 +12228,7 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
-        <v>12796</v>
+        <v>10844.06779661017</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -12126,8 +12239,9 @@
       <c r="W100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X100" s="3"/>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>1073</v>
       </c>
@@ -12186,7 +12300,7 @@
         <v>0</v>
       </c>
       <c r="T101" s="3">
-        <v>19597</v>
+        <v>16607.627118644068</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -12197,8 +12311,9 @@
       <c r="W101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X101" s="3"/>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1231</v>
       </c>
@@ -12257,7 +12372,7 @@
         <v>0</v>
       </c>
       <c r="T102" s="3">
-        <v>14495</v>
+        <v>12283.898305084746</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
@@ -12268,8 +12383,9 @@
       <c r="W102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X102" s="3"/>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>1177</v>
       </c>
@@ -12328,7 +12444,7 @@
         <v>0</v>
       </c>
       <c r="T103" s="3">
-        <v>12494</v>
+        <v>10588.135593220339</v>
       </c>
       <c r="U103" s="3">
         <v>0</v>
@@ -12339,8 +12455,9 @@
       <c r="W103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X103" s="3"/>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>1011</v>
       </c>
@@ -12399,7 +12516,7 @@
         <v>0</v>
       </c>
       <c r="T104" s="3">
-        <v>12495</v>
+        <v>10588.983050847459</v>
       </c>
       <c r="U104" s="3">
         <v>0</v>
@@ -12410,8 +12527,9 @@
       <c r="W104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X104" s="3"/>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>1193</v>
       </c>
@@ -12470,7 +12588,7 @@
         <v>0</v>
       </c>
       <c r="T105" s="3">
-        <v>24494</v>
+        <v>20757.627118644068</v>
       </c>
       <c r="U105" s="3">
         <v>0</v>
@@ -12481,8 +12599,9 @@
       <c r="W105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X105" s="3"/>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>1135</v>
       </c>
@@ -12541,7 +12660,7 @@
         <v>0</v>
       </c>
       <c r="T106" s="3">
-        <v>17147</v>
+        <v>14531.355932203391</v>
       </c>
       <c r="U106" s="3">
         <v>0</v>
@@ -12552,8 +12671,9 @@
       <c r="W106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X106" s="3"/>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1143</v>
       </c>
@@ -12612,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="T107" s="3">
-        <v>11495</v>
+        <v>9741.5254237288136</v>
       </c>
       <c r="U107" s="3">
         <v>0</v>
@@ -12623,8 +12743,9 @@
       <c r="W107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X107" s="3"/>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>1201</v>
       </c>
@@ -12683,7 +12804,7 @@
         <v>0</v>
       </c>
       <c r="T108" s="3">
-        <v>11995</v>
+        <v>10165.254237288136</v>
       </c>
       <c r="U108" s="3">
         <v>0</v>
@@ -12694,8 +12815,9 @@
       <c r="W108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X108" s="3"/>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>1043</v>
       </c>
@@ -12754,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="T109" s="3">
-        <v>15995</v>
+        <v>13555.084745762713</v>
       </c>
       <c r="U109" s="3">
         <v>0</v>
@@ -12765,8 +12887,9 @@
       <c r="W109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X109" s="3"/>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>1277</v>
       </c>
@@ -12825,7 +12948,7 @@
         <v>0</v>
       </c>
       <c r="T110" s="3">
-        <v>24495</v>
+        <v>20758.474576271186</v>
       </c>
       <c r="U110" s="3">
         <v>0</v>
@@ -12836,8 +12959,9 @@
       <c r="W110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X110" s="3"/>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>1203</v>
       </c>
@@ -12896,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="T111" s="3">
-        <v>15994</v>
+        <v>13554.237288135593</v>
       </c>
       <c r="U111" s="3">
         <v>0</v>
@@ -12907,8 +13031,9 @@
       <c r="W111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X111" s="3"/>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>1279</v>
       </c>
@@ -12967,7 +13092,7 @@
         <v>0</v>
       </c>
       <c r="T112" s="3">
-        <v>17495</v>
+        <v>14826.271186440679</v>
       </c>
       <c r="U112" s="3">
         <v>0</v>
@@ -12978,8 +13103,9 @@
       <c r="W112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X112" s="3"/>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>1283</v>
       </c>
@@ -13038,7 +13164,7 @@
         <v>0</v>
       </c>
       <c r="T113" s="3">
-        <v>19995</v>
+        <v>16944.91525423729</v>
       </c>
       <c r="U113" s="3">
         <v>0</v>
@@ -13049,8 +13175,9 @@
       <c r="W113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X113" s="3"/>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>1303</v>
       </c>
@@ -13109,7 +13236,7 @@
         <v>0</v>
       </c>
       <c r="T114" s="3">
-        <v>19995</v>
+        <v>16944.91525423729</v>
       </c>
       <c r="U114" s="3">
         <v>0</v>
@@ -13120,8 +13247,9 @@
       <c r="W114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X114" s="3"/>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>837</v>
       </c>
@@ -13191,8 +13319,9 @@
       <c r="W115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X115" s="3"/>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>1215</v>
       </c>
@@ -13262,8 +13391,9 @@
       <c r="W116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X116" s="3"/>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>1379</v>
       </c>
@@ -13333,8 +13463,9 @@
       <c r="W117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X117" s="3"/>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>891</v>
       </c>
@@ -13404,8 +13535,9 @@
       <c r="W118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X118" s="3"/>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>705</v>
       </c>
@@ -13475,8 +13607,9 @@
       <c r="W119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X119" s="3"/>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>703</v>
       </c>
@@ -13546,8 +13679,9 @@
       <c r="W120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X120" s="3"/>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>1059</v>
       </c>
@@ -13617,8 +13751,9 @@
       <c r="W121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X121" s="3"/>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>1147</v>
       </c>
@@ -13688,8 +13823,9 @@
       <c r="W122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X122" s="3"/>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>797</v>
       </c>
@@ -13759,8 +13895,9 @@
       <c r="W123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X123" s="3"/>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>1049</v>
       </c>
@@ -13830,8 +13967,9 @@
       <c r="W124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X124" s="3"/>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>1369</v>
       </c>
@@ -13901,8 +14039,9 @@
       <c r="W125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X125" s="3"/>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>1219</v>
       </c>
@@ -13972,8 +14111,9 @@
       <c r="W126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X126" s="3"/>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>943</v>
       </c>
@@ -14043,8 +14183,9 @@
       <c r="W127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X127" s="3"/>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>1097</v>
       </c>
@@ -14114,8 +14255,9 @@
       <c r="W128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X128" s="3"/>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>707</v>
       </c>
@@ -14185,8 +14327,9 @@
       <c r="W129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X129" s="3"/>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>1099</v>
       </c>
@@ -14256,8 +14399,9 @@
       <c r="W130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X130" s="3"/>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>1299</v>
       </c>
@@ -14327,8 +14471,9 @@
       <c r="W131">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X131" s="3"/>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>1301</v>
       </c>
@@ -14398,8 +14543,9 @@
       <c r="W132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X132" s="3"/>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>1015</v>
       </c>
@@ -14469,8 +14615,9 @@
       <c r="W133">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X133" s="3"/>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>1087</v>
       </c>
@@ -14540,8 +14687,9 @@
       <c r="W134">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X134" s="3"/>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>1093</v>
       </c>
@@ -14611,8 +14759,9 @@
       <c r="W135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X135" s="3"/>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>1221</v>
       </c>
@@ -14682,8 +14831,9 @@
       <c r="W136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X136" s="3"/>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>1195</v>
       </c>
@@ -14753,8 +14903,9 @@
       <c r="W137">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X137" s="3"/>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>1137</v>
       </c>
@@ -14824,8 +14975,9 @@
       <c r="W138">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X138" s="3"/>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>1125</v>
       </c>
@@ -14895,8 +15047,9 @@
       <c r="W139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X139" s="3"/>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>1227</v>
       </c>
@@ -14966,8 +15119,9 @@
       <c r="W140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X140" s="3"/>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>1123</v>
       </c>
@@ -15037,8 +15191,9 @@
       <c r="W141">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X141" s="3"/>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>1127</v>
       </c>
@@ -15108,8 +15263,9 @@
       <c r="W142">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X142" s="3"/>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>1013</v>
       </c>
@@ -15179,8 +15335,9 @@
       <c r="W143">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X143" s="3"/>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>1239</v>
       </c>
@@ -15250,8 +15407,9 @@
       <c r="W144">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X144" s="3"/>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>1025</v>
       </c>
@@ -15321,8 +15479,9 @@
       <c r="W145">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X145" s="3"/>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>1225</v>
       </c>
@@ -15392,8 +15551,9 @@
       <c r="W146">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X146" s="3"/>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>1241</v>
       </c>
@@ -15463,8 +15623,9 @@
       <c r="W147">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X147" s="3"/>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>973</v>
       </c>
@@ -15534,8 +15695,9 @@
       <c r="W148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X148" s="3"/>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>791</v>
       </c>
@@ -15605,8 +15767,9 @@
       <c r="W149">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X149" s="3"/>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>1243</v>
       </c>
@@ -15676,8 +15839,9 @@
       <c r="W150">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X150" s="3"/>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>1373</v>
       </c>
@@ -15747,8 +15911,9 @@
       <c r="W151">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X151" s="3"/>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>901</v>
       </c>
@@ -15818,8 +15983,9 @@
       <c r="W152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X152" s="3"/>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>1045</v>
       </c>
@@ -15889,8 +16055,9 @@
       <c r="W153">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X153" s="3"/>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>855</v>
       </c>
@@ -15960,8 +16127,9 @@
       <c r="W154">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X154" s="3"/>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>839</v>
       </c>
@@ -16031,8 +16199,9 @@
       <c r="W155">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X155" s="3"/>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>959</v>
       </c>
@@ -16102,8 +16271,9 @@
       <c r="W156">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X156" s="3"/>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>903</v>
       </c>
@@ -16173,8 +16343,9 @@
       <c r="W157">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X157" s="3"/>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>859</v>
       </c>
@@ -16244,8 +16415,9 @@
       <c r="W158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X158" s="3"/>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>873</v>
       </c>
@@ -16315,8 +16487,9 @@
       <c r="W159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X159" s="3"/>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>1165</v>
       </c>
@@ -16386,8 +16559,9 @@
       <c r="W160">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X160" s="3"/>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>1051</v>
       </c>
@@ -16457,8 +16631,9 @@
       <c r="W161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X161" s="3"/>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>993</v>
       </c>
@@ -16528,8 +16703,9 @@
       <c r="W162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X162" s="3"/>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>1263</v>
       </c>
@@ -16599,8 +16775,9 @@
       <c r="W163">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X163" s="3"/>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>1081</v>
       </c>
@@ -16670,8 +16847,9 @@
       <c r="W164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X164" s="3"/>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>933</v>
       </c>
@@ -16741,8 +16919,9 @@
       <c r="W165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X165" s="3"/>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>823</v>
       </c>
@@ -16812,8 +16991,9 @@
       <c r="W166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X166" s="3"/>
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>905</v>
       </c>
@@ -16883,8 +17063,9 @@
       <c r="W167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X167" s="3"/>
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>1029</v>
       </c>
@@ -16954,8 +17135,9 @@
       <c r="W168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X168" s="3"/>
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>979</v>
       </c>
@@ -17025,8 +17207,9 @@
       <c r="W169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X169" s="3"/>
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>861</v>
       </c>
@@ -17096,8 +17279,9 @@
       <c r="W170">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X170" s="3"/>
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>963</v>
       </c>
@@ -17167,8 +17351,9 @@
       <c r="W171">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X171" s="3"/>
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>1001</v>
       </c>
@@ -17238,8 +17423,9 @@
       <c r="W172">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X172" s="3"/>
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>1003</v>
       </c>
@@ -17309,8 +17495,9 @@
       <c r="W173">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X173" s="3"/>
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>767</v>
       </c>
@@ -17380,8 +17567,9 @@
       <c r="W174">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X174" s="3"/>
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>1273</v>
       </c>
@@ -17451,8 +17639,9 @@
       <c r="W175">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X175" s="3"/>
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>975</v>
       </c>
@@ -17522,8 +17711,9 @@
       <c r="W176">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X176" s="3"/>
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>935</v>
       </c>
@@ -17593,8 +17783,9 @@
       <c r="W177">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X177" s="3"/>
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>969</v>
       </c>
@@ -17664,8 +17855,9 @@
       <c r="W178">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X178" s="3"/>
+    </row>
+    <row r="179" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>1271</v>
       </c>
@@ -17735,8 +17927,9 @@
       <c r="W179">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X179" s="3"/>
+    </row>
+    <row r="180" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>939</v>
       </c>
@@ -17806,8 +17999,9 @@
       <c r="W180">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X180" s="3"/>
+    </row>
+    <row r="181" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>1151</v>
       </c>
@@ -17877,8 +18071,9 @@
       <c r="W181">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X181" s="3"/>
+    </row>
+    <row r="182" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>841</v>
       </c>
@@ -17948,8 +18143,9 @@
       <c r="W182">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X182" s="3"/>
+    </row>
+    <row r="183" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>1155</v>
       </c>
@@ -18019,8 +18215,9 @@
       <c r="W183">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X183" s="3"/>
+    </row>
+    <row r="184" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>1157</v>
       </c>
@@ -18090,8 +18287,9 @@
       <c r="W184">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X184" s="3"/>
+    </row>
+    <row r="185" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>977</v>
       </c>
@@ -18161,8 +18359,9 @@
       <c r="W185">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X185" s="3"/>
+    </row>
+    <row r="186" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>1041</v>
       </c>
@@ -18232,8 +18431,9 @@
       <c r="W186">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X186" s="3"/>
+    </row>
+    <row r="187" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>1035</v>
       </c>
@@ -18303,8 +18503,9 @@
       <c r="W187">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X187" s="3"/>
+    </row>
+    <row r="188" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>1217</v>
       </c>
@@ -18374,8 +18575,9 @@
       <c r="W188">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X188" s="3"/>
+    </row>
+    <row r="189" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>893</v>
       </c>
@@ -18445,8 +18647,9 @@
       <c r="W189">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X189" s="3"/>
+    </row>
+    <row r="190" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>783</v>
       </c>
@@ -18516,8 +18719,9 @@
       <c r="W190">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X190" s="3"/>
+    </row>
+    <row r="191" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>965</v>
       </c>
@@ -18587,8 +18791,9 @@
       <c r="W191">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X191" s="3"/>
+    </row>
+    <row r="192" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>1055</v>
       </c>
@@ -18658,8 +18863,9 @@
       <c r="W192">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X192" s="3"/>
+    </row>
+    <row r="193" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1163</v>
       </c>
@@ -18729,8 +18935,9 @@
       <c r="W193">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X193" s="3"/>
+    </row>
+    <row r="194" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>997</v>
       </c>
@@ -18800,8 +19007,9 @@
       <c r="W194">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X194" s="3"/>
+    </row>
+    <row r="195" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>941</v>
       </c>
@@ -18871,8 +19079,9 @@
       <c r="W195">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X195" s="3"/>
+    </row>
+    <row r="196" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>771</v>
       </c>
@@ -18942,8 +19151,9 @@
       <c r="W196">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X196" s="3"/>
+    </row>
+    <row r="197" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>1161</v>
       </c>
@@ -19013,8 +19223,9 @@
       <c r="W197">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X197" s="3"/>
+    </row>
+    <row r="198" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1091</v>
       </c>
@@ -19084,8 +19295,9 @@
       <c r="W198">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X198" s="3"/>
+    </row>
+    <row r="199" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1089</v>
       </c>
@@ -19155,8 +19367,9 @@
       <c r="W199">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X199" s="3"/>
+    </row>
+    <row r="200" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>1095</v>
       </c>
@@ -19226,8 +19439,9 @@
       <c r="W200">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X200" s="3"/>
+    </row>
+    <row r="201" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1063</v>
       </c>
@@ -19297,8 +19511,9 @@
       <c r="W201">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X201" s="3"/>
+    </row>
+    <row r="202" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>957</v>
       </c>
@@ -19368,8 +19583,9 @@
       <c r="W202">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X202" s="3"/>
+    </row>
+    <row r="203" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>897</v>
       </c>
@@ -19439,8 +19655,9 @@
       <c r="W203">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X203" s="3"/>
+    </row>
+    <row r="204" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1159</v>
       </c>
@@ -19510,8 +19727,9 @@
       <c r="W204">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X204" s="3"/>
+    </row>
+    <row r="205" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1229</v>
       </c>
@@ -19581,8 +19799,9 @@
       <c r="W205">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X205" s="3"/>
+    </row>
+    <row r="206" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>967</v>
       </c>
@@ -19652,8 +19871,9 @@
       <c r="W206">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X206" s="3"/>
+    </row>
+    <row r="207" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>907</v>
       </c>
@@ -19723,8 +19943,9 @@
       <c r="W207">
         <v>0</v>
       </c>
-    </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X207" s="3"/>
+    </row>
+    <row r="208" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1269</v>
       </c>
@@ -19794,8 +20015,9 @@
       <c r="W208">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X208" s="3"/>
+    </row>
+    <row r="209" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>949</v>
       </c>
@@ -19865,8 +20087,9 @@
       <c r="W209">
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X209" s="3"/>
+    </row>
+    <row r="210" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>1061</v>
       </c>
@@ -19936,8 +20159,9 @@
       <c r="W210">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X210" s="3"/>
+    </row>
+    <row r="211" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>909</v>
       </c>
@@ -20007,8 +20231,9 @@
       <c r="W211">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X211" s="3"/>
+    </row>
+    <row r="212" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>1021</v>
       </c>
@@ -20078,8 +20303,9 @@
       <c r="W212">
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X212" s="3"/>
+    </row>
+    <row r="213" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>747</v>
       </c>
@@ -20149,8 +20375,9 @@
       <c r="W213">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X213" s="3"/>
+    </row>
+    <row r="214" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>961</v>
       </c>
@@ -20220,8 +20447,9 @@
       <c r="W214">
         <v>0</v>
       </c>
-    </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X214" s="3"/>
+    </row>
+    <row r="215" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>1037</v>
       </c>
@@ -20291,8 +20519,9 @@
       <c r="W215">
         <v>0</v>
       </c>
-    </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X215" s="3"/>
+    </row>
+    <row r="216" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>845</v>
       </c>
@@ -20362,8 +20591,9 @@
       <c r="W216">
         <v>0</v>
       </c>
-    </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X216" s="3"/>
+    </row>
+    <row r="217" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>1023</v>
       </c>
@@ -20433,8 +20663,9 @@
       <c r="W217">
         <v>0</v>
       </c>
-    </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X217" s="3"/>
+    </row>
+    <row r="218" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>829</v>
       </c>
@@ -20504,8 +20735,9 @@
       <c r="W218">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X218" s="3"/>
+    </row>
+    <row r="219" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>899</v>
       </c>
@@ -20575,8 +20807,9 @@
       <c r="W219">
         <v>0</v>
       </c>
-    </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X219" s="3"/>
+    </row>
+    <row r="220" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>1101</v>
       </c>
@@ -20646,8 +20879,9 @@
       <c r="W220">
         <v>0</v>
       </c>
-    </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X220" s="3"/>
+    </row>
+    <row r="221" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>863</v>
       </c>
@@ -20717,8 +20951,9 @@
       <c r="W221">
         <v>0</v>
       </c>
-    </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X221" s="3"/>
+    </row>
+    <row r="222" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>931</v>
       </c>
@@ -20788,8 +21023,9 @@
       <c r="W222">
         <v>0</v>
       </c>
-    </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X222" s="3"/>
+    </row>
+    <row r="223" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>1153</v>
       </c>
@@ -20859,8 +21095,9 @@
       <c r="W223">
         <v>0</v>
       </c>
-    </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X223" s="3"/>
+    </row>
+    <row r="224" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>981</v>
       </c>
@@ -20930,8 +21167,9 @@
       <c r="W224">
         <v>0</v>
       </c>
-    </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X224" s="3"/>
+    </row>
+    <row r="225" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>867</v>
       </c>
@@ -21001,8 +21239,9 @@
       <c r="W225">
         <v>0</v>
       </c>
-    </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X225" s="3"/>
+    </row>
+    <row r="226" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>1083</v>
       </c>
@@ -21072,8 +21311,9 @@
       <c r="W226">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X226" s="3"/>
+    </row>
+    <row r="227" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>1145</v>
       </c>
@@ -21143,8 +21383,9 @@
       <c r="W227">
         <v>0</v>
       </c>
-    </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X227" s="3"/>
+    </row>
+    <row r="228" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>1071</v>
       </c>
@@ -21214,8 +21455,9 @@
       <c r="W228">
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X228" s="3"/>
+    </row>
+    <row r="229" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>1069</v>
       </c>
@@ -21285,8 +21527,9 @@
       <c r="W229">
         <v>0</v>
       </c>
-    </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X229" s="3"/>
+    </row>
+    <row r="230" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>945</v>
       </c>
@@ -21356,8 +21599,9 @@
       <c r="W230">
         <v>0</v>
       </c>
-    </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X230" s="3"/>
+    </row>
+    <row r="231" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>877</v>
       </c>
@@ -21427,8 +21671,9 @@
       <c r="W231">
         <v>0</v>
       </c>
-    </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X231" s="3"/>
+    </row>
+    <row r="232" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1075</v>
       </c>
@@ -21498,8 +21743,9 @@
       <c r="W232">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X232" s="3"/>
+    </row>
+    <row r="233" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>951</v>
       </c>
@@ -21569,8 +21815,9 @@
       <c r="W233">
         <v>0</v>
       </c>
-    </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X233" s="3"/>
+    </row>
+    <row r="234" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>913</v>
       </c>
@@ -21640,8 +21887,9 @@
       <c r="W234">
         <v>0</v>
       </c>
-    </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X234" s="3"/>
+    </row>
+    <row r="235" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1233</v>
       </c>
@@ -21711,8 +21959,9 @@
       <c r="W235">
         <v>0</v>
       </c>
-    </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X235" s="3"/>
+    </row>
+    <row r="236" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1105</v>
       </c>
@@ -21782,8 +22031,9 @@
       <c r="W236">
         <v>0</v>
       </c>
-    </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X236" s="3"/>
+    </row>
+    <row r="237" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1235</v>
       </c>
@@ -21853,8 +22103,9 @@
       <c r="W237">
         <v>0</v>
       </c>
-    </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X237" s="3"/>
+    </row>
+    <row r="238" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>1107</v>
       </c>
@@ -21924,8 +22175,9 @@
       <c r="W238">
         <v>0</v>
       </c>
-    </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X238" s="3"/>
+    </row>
+    <row r="239" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1077</v>
       </c>
@@ -21995,8 +22247,9 @@
       <c r="W239">
         <v>0</v>
       </c>
-    </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X239" s="3"/>
+    </row>
+    <row r="240" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>795</v>
       </c>
@@ -22066,8 +22319,9 @@
       <c r="W240">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X240" s="3"/>
+    </row>
+    <row r="241" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1103</v>
       </c>
@@ -22137,8 +22391,9 @@
       <c r="W241">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X241" s="3"/>
+    </row>
+    <row r="242" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>985</v>
       </c>
@@ -22208,8 +22463,9 @@
       <c r="W242">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X242" s="3"/>
+    </row>
+    <row r="243" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1265</v>
       </c>
@@ -22279,8 +22535,9 @@
       <c r="W243">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X243" s="3"/>
+    </row>
+    <row r="244" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1237</v>
       </c>
@@ -22350,8 +22607,9 @@
       <c r="W244">
         <v>0</v>
       </c>
-    </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X244" s="3"/>
+    </row>
+    <row r="245" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>989</v>
       </c>
@@ -22421,8 +22679,9 @@
       <c r="W245">
         <v>0</v>
       </c>
-    </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X245" s="3"/>
+    </row>
+    <row r="246" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>983</v>
       </c>
@@ -22492,8 +22751,9 @@
       <c r="W246">
         <v>0</v>
       </c>
-    </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X246" s="3"/>
+    </row>
+    <row r="247" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>847</v>
       </c>
@@ -22563,8 +22823,9 @@
       <c r="W247">
         <v>0</v>
       </c>
-    </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X247" s="3"/>
+    </row>
+    <row r="248" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>1119</v>
       </c>
@@ -22634,8 +22895,9 @@
       <c r="W248">
         <v>0</v>
       </c>
-    </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X248" s="3"/>
+    </row>
+    <row r="249" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>1121</v>
       </c>
@@ -22705,8 +22967,9 @@
       <c r="W249">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X249" s="3"/>
+    </row>
+    <row r="250" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1169</v>
       </c>
@@ -22776,8 +23039,9 @@
       <c r="W250">
         <v>0</v>
       </c>
-    </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X250" s="3"/>
+    </row>
+    <row r="251" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1167</v>
       </c>
@@ -22847,8 +23111,9 @@
       <c r="W251">
         <v>0</v>
       </c>
-    </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X251" s="3"/>
+    </row>
+    <row r="252" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1117</v>
       </c>
@@ -22918,8 +23183,9 @@
       <c r="W252">
         <v>0</v>
       </c>
-    </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X252" s="3"/>
+    </row>
+    <row r="253" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>881</v>
       </c>
@@ -22989,8 +23255,9 @@
       <c r="W253">
         <v>0</v>
       </c>
-    </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X253" s="3"/>
+    </row>
+    <row r="254" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>813</v>
       </c>
@@ -23060,8 +23327,9 @@
       <c r="W254">
         <v>0</v>
       </c>
-    </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X254" s="3"/>
+    </row>
+    <row r="255" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1017</v>
       </c>
@@ -23131,8 +23399,9 @@
       <c r="W255">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X255" s="3"/>
+    </row>
+    <row r="256" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>1133</v>
       </c>
@@ -23202,8 +23471,9 @@
       <c r="W256">
         <v>0</v>
       </c>
-    </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X256" s="3"/>
+    </row>
+    <row r="257" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>879</v>
       </c>
@@ -23273,8 +23543,9 @@
       <c r="W257">
         <v>0</v>
       </c>
-    </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X257" s="3"/>
+    </row>
+    <row r="258" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1179</v>
       </c>
@@ -23344,8 +23615,9 @@
       <c r="W258">
         <v>0</v>
       </c>
-    </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X258" s="3"/>
+    </row>
+    <row r="259" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>831</v>
       </c>
@@ -23415,8 +23687,9 @@
       <c r="W259">
         <v>0</v>
       </c>
-    </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X259" s="3"/>
+    </row>
+    <row r="260" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>827</v>
       </c>
@@ -23486,8 +23759,9 @@
       <c r="W260">
         <v>0</v>
       </c>
-    </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X260" s="3"/>
+    </row>
+    <row r="261" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>915</v>
       </c>
@@ -23557,8 +23831,9 @@
       <c r="W261">
         <v>0</v>
       </c>
-    </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X261" s="3"/>
+    </row>
+    <row r="262" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1131</v>
       </c>
@@ -23628,8 +23903,9 @@
       <c r="W262">
         <v>0</v>
       </c>
-    </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X262" s="3"/>
+    </row>
+    <row r="263" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1009</v>
       </c>
@@ -23699,8 +23975,9 @@
       <c r="W263">
         <v>0</v>
       </c>
-    </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X263" s="3"/>
+    </row>
+    <row r="264" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>849</v>
       </c>
@@ -23770,8 +24047,9 @@
       <c r="W264">
         <v>0</v>
       </c>
-    </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X264" s="3"/>
+    </row>
+    <row r="265" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1173</v>
       </c>
@@ -23841,8 +24119,9 @@
       <c r="W265">
         <v>0</v>
       </c>
-    </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X265" s="3"/>
+    </row>
+    <row r="266" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1005</v>
       </c>
@@ -23912,8 +24191,9 @@
       <c r="W266">
         <v>0</v>
       </c>
-    </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X266" s="3"/>
+    </row>
+    <row r="267" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1007</v>
       </c>
@@ -23983,8 +24263,9 @@
       <c r="W267">
         <v>0</v>
       </c>
-    </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X267" s="3"/>
+    </row>
+    <row r="268" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1171</v>
       </c>
@@ -24054,8 +24335,9 @@
       <c r="W268">
         <v>0</v>
       </c>
-    </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X268" s="3"/>
+    </row>
+    <row r="269" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>995</v>
       </c>
@@ -24125,8 +24407,9 @@
       <c r="W269">
         <v>0</v>
       </c>
-    </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X269" s="3"/>
+    </row>
+    <row r="270" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1129</v>
       </c>
@@ -24196,8 +24479,9 @@
       <c r="W270">
         <v>0</v>
       </c>
-    </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X270" s="3"/>
+    </row>
+    <row r="271" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>991</v>
       </c>
@@ -24267,8 +24551,9 @@
       <c r="W271">
         <v>0</v>
       </c>
-    </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X271" s="3"/>
+    </row>
+    <row r="272" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>999</v>
       </c>
@@ -24338,8 +24623,9 @@
       <c r="W272">
         <v>0</v>
       </c>
-    </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X272" s="3"/>
+    </row>
+    <row r="273" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>851</v>
       </c>
@@ -24409,8 +24695,9 @@
       <c r="W273">
         <v>0</v>
       </c>
-    </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X273" s="3"/>
+    </row>
+    <row r="274" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1175</v>
       </c>
@@ -24480,8 +24767,9 @@
       <c r="W274">
         <v>0</v>
       </c>
-    </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X274" s="3"/>
+    </row>
+    <row r="275" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1027</v>
       </c>
@@ -24551,8 +24839,9 @@
       <c r="W275">
         <v>0</v>
       </c>
-    </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X275" s="3"/>
+    </row>
+    <row r="276" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1019</v>
       </c>
@@ -24622,8 +24911,9 @@
       <c r="W276">
         <v>0</v>
       </c>
-    </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X276" s="3"/>
+    </row>
+    <row r="277" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1033</v>
       </c>
@@ -24693,8 +24983,9 @@
       <c r="W277">
         <v>0</v>
       </c>
-    </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X277" s="3"/>
+    </row>
+    <row r="278" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1189</v>
       </c>
@@ -24764,8 +25055,9 @@
       <c r="W278">
         <v>0</v>
       </c>
-    </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X278" s="3"/>
+    </row>
+    <row r="279" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1191</v>
       </c>
@@ -24835,8 +25127,9 @@
       <c r="W279">
         <v>0</v>
       </c>
-    </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X279" s="3"/>
+    </row>
+    <row r="280" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1187</v>
       </c>
@@ -24906,8 +25199,9 @@
       <c r="W280">
         <v>0</v>
       </c>
-    </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X280" s="3"/>
+    </row>
+    <row r="281" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1183</v>
       </c>
@@ -24977,8 +25271,9 @@
       <c r="W281">
         <v>0</v>
       </c>
-    </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X281" s="3"/>
+    </row>
+    <row r="282" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1181</v>
       </c>
@@ -25048,8 +25343,9 @@
       <c r="W282">
         <v>0</v>
       </c>
-    </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X282" s="3"/>
+    </row>
+    <row r="283" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1185</v>
       </c>
@@ -25119,8 +25415,9 @@
       <c r="W283">
         <v>0</v>
       </c>
-    </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X283" s="3"/>
+    </row>
+    <row r="284" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1255</v>
       </c>
@@ -25190,8 +25487,9 @@
       <c r="W284">
         <v>0</v>
       </c>
-    </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X284" s="3"/>
+    </row>
+    <row r="285" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1213</v>
       </c>
@@ -25261,8 +25559,9 @@
       <c r="W285">
         <v>0</v>
       </c>
-    </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X285" s="3"/>
+    </row>
+    <row r="286" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1207</v>
       </c>
@@ -25332,8 +25631,9 @@
       <c r="W286">
         <v>0</v>
       </c>
-    </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X286" s="3"/>
+    </row>
+    <row r="287" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1259</v>
       </c>
@@ -25403,8 +25703,9 @@
       <c r="W287">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X287" s="3"/>
+    </row>
+    <row r="288" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1249</v>
       </c>
@@ -25474,8 +25775,9 @@
       <c r="W288">
         <v>0</v>
       </c>
-    </row>
-    <row r="289" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X288" s="3"/>
+    </row>
+    <row r="289" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>883</v>
       </c>
@@ -25545,8 +25847,9 @@
       <c r="W289">
         <v>0</v>
       </c>
-    </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X289" s="3"/>
+    </row>
+    <row r="290" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>815</v>
       </c>
@@ -25616,8 +25919,9 @@
       <c r="W290">
         <v>0</v>
       </c>
-    </row>
-    <row r="291" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X290" s="3"/>
+    </row>
+    <row r="291" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1199</v>
       </c>
@@ -25687,8 +25991,9 @@
       <c r="W291">
         <v>0</v>
       </c>
-    </row>
-    <row r="292" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X291" s="3"/>
+    </row>
+    <row r="292" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>769</v>
       </c>
@@ -25758,8 +26063,9 @@
       <c r="W292">
         <v>0</v>
       </c>
-    </row>
-    <row r="293" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X292" s="3"/>
+    </row>
+    <row r="293" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>857</v>
       </c>
@@ -25829,8 +26135,9 @@
       <c r="W293">
         <v>0</v>
       </c>
-    </row>
-    <row r="294" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X293" s="3"/>
+    </row>
+    <row r="294" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1209</v>
       </c>
@@ -25900,8 +26207,9 @@
       <c r="W294">
         <v>0</v>
       </c>
-    </row>
-    <row r="295" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X294" s="3"/>
+    </row>
+    <row r="295" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>1275</v>
       </c>
@@ -25971,8 +26279,9 @@
       <c r="W295">
         <v>0</v>
       </c>
-    </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X295" s="3"/>
+    </row>
+    <row r="296" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>817</v>
       </c>
@@ -26042,8 +26351,9 @@
       <c r="W296">
         <v>0</v>
       </c>
-    </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X296" s="3"/>
+    </row>
+    <row r="297" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>885</v>
       </c>
@@ -26113,8 +26423,9 @@
       <c r="W297">
         <v>0</v>
       </c>
-    </row>
-    <row r="298" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X297" s="3"/>
+    </row>
+    <row r="298" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>1141</v>
       </c>
@@ -26184,8 +26495,9 @@
       <c r="W298">
         <v>0</v>
       </c>
-    </row>
-    <row r="299" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X298" s="3"/>
+    </row>
+    <row r="299" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>833</v>
       </c>
@@ -26255,8 +26567,9 @@
       <c r="W299">
         <v>0</v>
       </c>
-    </row>
-    <row r="300" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X299" s="3"/>
+    </row>
+    <row r="300" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1253</v>
       </c>
@@ -26326,8 +26639,9 @@
       <c r="W300">
         <v>0</v>
       </c>
-    </row>
-    <row r="301" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X300" s="3"/>
+    </row>
+    <row r="301" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1211</v>
       </c>
@@ -26397,8 +26711,9 @@
       <c r="W301">
         <v>0</v>
       </c>
-    </row>
-    <row r="302" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X301" s="3"/>
+    </row>
+    <row r="302" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1139</v>
       </c>
@@ -26468,8 +26783,9 @@
       <c r="W302">
         <v>0</v>
       </c>
-    </row>
-    <row r="303" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X302" s="3"/>
+    </row>
+    <row r="303" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1257</v>
       </c>
@@ -26539,8 +26855,9 @@
       <c r="W303">
         <v>0</v>
       </c>
-    </row>
-    <row r="304" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X303" s="3"/>
+    </row>
+    <row r="304" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>1197</v>
       </c>
@@ -26610,8 +26927,9 @@
       <c r="W304">
         <v>0</v>
       </c>
-    </row>
-    <row r="305" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X304" s="3"/>
+    </row>
+    <row r="305" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1039</v>
       </c>
@@ -26681,8 +26999,9 @@
       <c r="W305">
         <v>0</v>
       </c>
-    </row>
-    <row r="306" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X305" s="3"/>
+    </row>
+    <row r="306" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1251</v>
       </c>
@@ -26752,8 +27071,9 @@
       <c r="W306">
         <v>0</v>
       </c>
-    </row>
-    <row r="307" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X306" s="3"/>
+    </row>
+    <row r="307" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1245</v>
       </c>
@@ -26823,8 +27143,9 @@
       <c r="W307">
         <v>0</v>
       </c>
-    </row>
-    <row r="308" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X307" s="3"/>
+    </row>
+    <row r="308" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1341</v>
       </c>
@@ -26894,8 +27215,9 @@
       <c r="W308">
         <v>0</v>
       </c>
-    </row>
-    <row r="309" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X308" s="3"/>
+    </row>
+    <row r="309" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1287</v>
       </c>
@@ -26965,8 +27287,9 @@
       <c r="W309">
         <v>0</v>
       </c>
-    </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X309" s="3"/>
+    </row>
+    <row r="310" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1345</v>
       </c>
@@ -27036,8 +27359,9 @@
       <c r="W310">
         <v>0</v>
       </c>
-    </row>
-    <row r="311" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X310" s="3"/>
+    </row>
+    <row r="311" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>1285</v>
       </c>
@@ -27107,8 +27431,9 @@
       <c r="W311">
         <v>0</v>
       </c>
-    </row>
-    <row r="312" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X311" s="3"/>
+    </row>
+    <row r="312" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1349</v>
       </c>
@@ -27178,8 +27503,9 @@
       <c r="W312">
         <v>0</v>
       </c>
-    </row>
-    <row r="313" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X312" s="3"/>
+    </row>
+    <row r="313" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1335</v>
       </c>
@@ -27249,8 +27575,9 @@
       <c r="W313">
         <v>0</v>
       </c>
-    </row>
-    <row r="314" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X313" s="3"/>
+    </row>
+    <row r="314" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1347</v>
       </c>
@@ -27320,8 +27647,9 @@
       <c r="W314">
         <v>0</v>
       </c>
-    </row>
-    <row r="315" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X314" s="3"/>
+    </row>
+    <row r="315" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>1337</v>
       </c>
@@ -27391,8 +27719,9 @@
       <c r="W315">
         <v>0</v>
       </c>
-    </row>
-    <row r="316" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X315" s="3"/>
+    </row>
+    <row r="316" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>1295</v>
       </c>
@@ -27462,8 +27791,9 @@
       <c r="W316">
         <v>0</v>
       </c>
-    </row>
-    <row r="317" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X316" s="3"/>
+    </row>
+    <row r="317" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>1333</v>
       </c>
@@ -27533,8 +27863,9 @@
       <c r="W317">
         <v>0</v>
       </c>
-    </row>
-    <row r="318" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X317" s="3"/>
+    </row>
+    <row r="318" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>1289</v>
       </c>
@@ -27604,8 +27935,9 @@
       <c r="W318">
         <v>0</v>
       </c>
-    </row>
-    <row r="319" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X318" s="3"/>
+    </row>
+    <row r="319" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>1297</v>
       </c>
@@ -27675,8 +28007,9 @@
       <c r="W319">
         <v>0</v>
       </c>
-    </row>
-    <row r="320" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X319" s="3"/>
+    </row>
+    <row r="320" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>1293</v>
       </c>
@@ -27746,8 +28079,9 @@
       <c r="W320">
         <v>0</v>
       </c>
-    </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X320" s="3"/>
+    </row>
+    <row r="321" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>1281</v>
       </c>
@@ -27817,8 +28151,9 @@
       <c r="W321">
         <v>0</v>
       </c>
-    </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X321" s="3"/>
+    </row>
+    <row r="322" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>1361</v>
       </c>
@@ -27888,8 +28223,9 @@
       <c r="W322">
         <v>0</v>
       </c>
-    </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X322" s="3"/>
+    </row>
+    <row r="323" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>1323</v>
       </c>
@@ -27959,8 +28295,9 @@
       <c r="W323">
         <v>0</v>
       </c>
-    </row>
-    <row r="324" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X323" s="3"/>
+    </row>
+    <row r="324" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>1307</v>
       </c>
@@ -28030,8 +28367,9 @@
       <c r="W324">
         <v>0</v>
       </c>
-    </row>
-    <row r="325" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X324" s="3"/>
+    </row>
+    <row r="325" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>1363</v>
       </c>
@@ -28101,8 +28439,9 @@
       <c r="W325">
         <v>0</v>
       </c>
-    </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X325" s="3"/>
+    </row>
+    <row r="326" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>1319</v>
       </c>
@@ -28172,8 +28511,9 @@
       <c r="W326">
         <v>0</v>
       </c>
-    </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X326" s="3"/>
+    </row>
+    <row r="327" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>1329</v>
       </c>
@@ -28243,8 +28583,9 @@
       <c r="W327">
         <v>0</v>
       </c>
-    </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X327" s="3"/>
+    </row>
+    <row r="328" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>1355</v>
       </c>
@@ -28314,8 +28655,9 @@
       <c r="W328">
         <v>0</v>
       </c>
-    </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X328" s="3"/>
+    </row>
+    <row r="329" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>1317</v>
       </c>
@@ -28385,8 +28727,9 @@
       <c r="W329">
         <v>0</v>
       </c>
-    </row>
-    <row r="330" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X329" s="3"/>
+    </row>
+    <row r="330" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>1351</v>
       </c>
@@ -28456,8 +28799,9 @@
       <c r="W330">
         <v>0</v>
       </c>
-    </row>
-    <row r="331" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X330" s="3"/>
+    </row>
+    <row r="331" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>1311</v>
       </c>
@@ -28527,8 +28871,9 @@
       <c r="W331">
         <v>0</v>
       </c>
-    </row>
-    <row r="332" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X331" s="3"/>
+    </row>
+    <row r="332" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>1359</v>
       </c>
@@ -28598,8 +28943,9 @@
       <c r="W332">
         <v>0</v>
       </c>
-    </row>
-    <row r="333" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X332" s="3"/>
+    </row>
+    <row r="333" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>1309</v>
       </c>
@@ -28669,8 +29015,9 @@
       <c r="W333">
         <v>0</v>
       </c>
-    </row>
-    <row r="334" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X333" s="3"/>
+    </row>
+    <row r="334" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>1357</v>
       </c>
@@ -28740,8 +29087,9 @@
       <c r="W334">
         <v>0</v>
       </c>
-    </row>
-    <row r="335" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X334" s="3"/>
+    </row>
+    <row r="335" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1327</v>
       </c>
@@ -28811,8 +29159,9 @@
       <c r="W335">
         <v>0</v>
       </c>
-    </row>
-    <row r="336" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X335" s="3"/>
+    </row>
+    <row r="336" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1325</v>
       </c>
@@ -28882,8 +29231,9 @@
       <c r="W336">
         <v>0</v>
       </c>
-    </row>
-    <row r="337" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X336" s="3"/>
+    </row>
+    <row r="337" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1313</v>
       </c>
@@ -28953,8 +29303,9 @@
       <c r="W337">
         <v>0</v>
       </c>
-    </row>
-    <row r="338" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X337" s="3"/>
+    </row>
+    <row r="338" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1291</v>
       </c>
@@ -29024,8 +29375,9 @@
       <c r="W338">
         <v>0</v>
       </c>
-    </row>
-    <row r="339" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X338" s="3"/>
+    </row>
+    <row r="339" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1353</v>
       </c>
@@ -29095,8 +29447,9 @@
       <c r="W339">
         <v>0</v>
       </c>
-    </row>
-    <row r="340" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X339" s="3"/>
+    </row>
+    <row r="340" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1321</v>
       </c>
@@ -29166,8 +29519,9 @@
       <c r="W340">
         <v>0</v>
       </c>
-    </row>
-    <row r="341" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X340" s="3"/>
+    </row>
+    <row r="341" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1339</v>
       </c>
@@ -29237,8 +29591,9 @@
       <c r="W341">
         <v>0</v>
       </c>
-    </row>
-    <row r="342" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X341" s="3"/>
+    </row>
+    <row r="342" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1305</v>
       </c>
@@ -29308,6 +29663,7 @@
       <c r="W342">
         <v>0</v>
       </c>
+      <c r="X342" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
